--- a/AAII_Financials/Quarterly/NCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
   <si>
     <t>NCT</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,148 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F8" s="3">
         <v>6600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>6600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>6200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>6200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>6400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>6400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>9900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F9" s="3">
         <v>4600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>4600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>4500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>4500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>4100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>4100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>4900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F10" s="3">
         <v>2000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +834,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -826,11 +853,11 @@
       <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
+      <c r="H12" s="3">
+        <v>200</v>
+      </c>
+      <c r="I12" s="3">
+        <v>200</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -838,8 +865,14 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,8 +900,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -896,8 +935,14 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -920,13 +965,19 @@
         <v>900</v>
       </c>
       <c r="J15" s="3">
+        <v>900</v>
+      </c>
+      <c r="K15" s="3">
+        <v>900</v>
+      </c>
+      <c r="L15" s="3">
         <v>800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,45 +986,53 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F17" s="3">
         <v>5300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>5200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="E18" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="F18" s="3">
         <v>1300</v>
@@ -982,19 +1041,25 @@
         <v>1300</v>
       </c>
       <c r="H18" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J18" s="3">
         <v>2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>2100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>4600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,23 +1071,25 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1035,45 +1102,57 @@
       <c r="K20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F21" s="3">
         <v>2400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>2200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>3000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>3000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>5400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E22" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F22" s="3">
         <v>700</v>
@@ -1082,27 +1161,33 @@
         <v>700</v>
       </c>
       <c r="H22" s="3">
+        <v>700</v>
+      </c>
+      <c r="I22" s="3">
+        <v>700</v>
+      </c>
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E23" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="F23" s="3">
         <v>800</v>
@@ -1111,19 +1196,25 @@
         <v>800</v>
       </c>
       <c r="H23" s="3">
+        <v>800</v>
+      </c>
+      <c r="I23" s="3">
+        <v>800</v>
+      </c>
+      <c r="J23" s="3">
         <v>1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>4000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1242,14 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,16 +1277,22 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E26" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="F26" s="3">
         <v>800</v>
@@ -1198,27 +1301,33 @@
         <v>800</v>
       </c>
       <c r="H26" s="3">
+        <v>800</v>
+      </c>
+      <c r="I26" s="3">
+        <v>800</v>
+      </c>
+      <c r="J26" s="3">
         <v>1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>4000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E27" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="F27" s="3">
         <v>800</v>
@@ -1227,19 +1336,25 @@
         <v>800</v>
       </c>
       <c r="H27" s="3">
+        <v>800</v>
+      </c>
+      <c r="I27" s="3">
+        <v>800</v>
+      </c>
+      <c r="J27" s="3">
         <v>1400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>4000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1382,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1417,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1452,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,23 +1487,29 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -1383,16 +1522,22 @@
       <c r="K32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E33" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="F33" s="3">
         <v>800</v>
@@ -1401,19 +1546,25 @@
         <v>800</v>
       </c>
       <c r="H33" s="3">
+        <v>800</v>
+      </c>
+      <c r="I33" s="3">
+        <v>800</v>
+      </c>
+      <c r="J33" s="3">
         <v>1400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>4000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,16 +1592,22 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E35" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="F35" s="3">
         <v>800</v>
@@ -1459,53 +1616,65 @@
         <v>800</v>
       </c>
       <c r="H35" s="3">
+        <v>800</v>
+      </c>
+      <c r="I35" s="3">
+        <v>800</v>
+      </c>
+      <c r="J35" s="3">
         <v>1400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>4000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1686,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,37 +1701,45 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F41" s="3">
         <v>3800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3400</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,37 +1767,49 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>12700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>12700</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1646,8 +1837,14 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1657,55 +1854,67 @@
       <c r="E45" s="3">
         <v>600</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="F45" s="3">
+        <v>600</v>
+      </c>
+      <c r="G45" s="3">
+        <v>600</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F46" s="3">
         <v>5100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>16600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>16600</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1733,37 +1942,49 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>54500</v>
+      </c>
+      <c r="F48" s="3">
         <v>57800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>57800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>61100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>61100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>62300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>62300</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1791,8 +2012,14 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2047,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,8 +2082,14 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1872,14 +2111,20 @@
       <c r="I52" s="3">
         <v>1000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="J52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2152,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>63300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>63300</v>
+      </c>
+      <c r="F54" s="3">
         <v>65100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>65100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>69000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>69000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>80200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>80200</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2206,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,8 +2221,10 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -1974,25 +2235,31 @@
         <v>1000</v>
       </c>
       <c r="F57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2003,10 +2270,10 @@
         <v>7900</v>
       </c>
       <c r="F58" s="3">
-        <v>8200</v>
+        <v>7900</v>
       </c>
       <c r="G58" s="3">
-        <v>8200</v>
+        <v>7900</v>
       </c>
       <c r="H58" s="3">
         <v>8200</v>
@@ -2015,129 +2282,159 @@
         <v>8200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+        <v>8200</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>26200</v>
+      </c>
+      <c r="F59" s="3">
         <v>26100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>26100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>26900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>26900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>25500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>25500</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>35700</v>
+      </c>
+      <c r="F60" s="3">
         <v>35400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>35400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>36500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>36500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>34600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>34600</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>14400</v>
+      </c>
+      <c r="F61" s="3">
         <v>18400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>18400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>23100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>23100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>27200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>27200</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3">
         <v>400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2462,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2497,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2532,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>50100</v>
+      </c>
+      <c r="F66" s="3">
         <v>54200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>54200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>61000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>61000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>62300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>62300</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2586,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2617,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2652,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2687,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2722,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F72" s="3">
         <v>9300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>9300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>7900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>7900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>17900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>17900</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2792,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2827,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2862,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F76" s="3">
         <v>10900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>10900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>7900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>7900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>18000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>18000</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M76" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,50 +2932,62 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E81" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="F81" s="3">
         <v>800</v>
@@ -2607,19 +2996,25 @@
         <v>800</v>
       </c>
       <c r="H81" s="3">
+        <v>800</v>
+      </c>
+      <c r="I81" s="3">
+        <v>800</v>
+      </c>
+      <c r="J81" s="3">
         <v>1400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>4000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,8 +3026,10 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2643,25 +3040,31 @@
         <v>1600</v>
       </c>
       <c r="F83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H83" s="3">
         <v>1500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1500</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3092,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3127,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3162,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3197,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3232,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F89" s="3">
         <v>1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>4500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,8 +3286,10 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2859,10 +3300,10 @@
         <v>-300</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -2871,13 +3312,19 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-6000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3352,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,28 +3387,34 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>5600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>5600</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-6000</v>
       </c>
       <c r="J94" s="3">
         <v>-6000</v>
@@ -2963,8 +3422,14 @@
       <c r="K94" s="3">
         <v>-6000</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="M94" s="3">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,37 +3441,45 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>5800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>5800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>1200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3507,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3542,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,37 +3577,49 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-6900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-6900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>3800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3150,33 +3647,45 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-5800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-5800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>2300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>2300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NCT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>NCT</t>
   </si>
@@ -656,199 +656,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F8" s="3">
         <v>5900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>5900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>6700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>6700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>6600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>6600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>6200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>6200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>6400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>6400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>9900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F9" s="3">
         <v>3900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>4800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>4800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>4600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>4600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>4500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>4500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>4100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>4100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>4900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F10" s="3">
         <v>2000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>4900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,22 +889,24 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>300</v>
+      </c>
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>200</v>
       </c>
       <c r="H12" s="3">
         <v>200</v>
@@ -893,11 +920,11 @@
       <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
+      <c r="L12" s="3">
+        <v>200</v>
+      </c>
+      <c r="M12" s="3">
+        <v>200</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -905,8 +932,14 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +979,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1026,14 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1023,13 +1068,19 @@
         <v>900</v>
       </c>
       <c r="N15" s="3">
+        <v>900</v>
+      </c>
+      <c r="O15" s="3">
+        <v>900</v>
+      </c>
+      <c r="P15" s="3">
         <v>800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,69 +1093,77 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F17" s="3">
         <v>4500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>5600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>5200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F18" s="3">
         <v>1400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1300</v>
       </c>
       <c r="J18" s="3">
         <v>1300</v>
@@ -1113,19 +1172,25 @@
         <v>1300</v>
       </c>
       <c r="L18" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M18" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N18" s="3">
         <v>2100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>2100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>4600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,35 +1206,37 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1182,69 +1249,81 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>200</v>
+      </c>
+      <c r="F21" s="3">
         <v>2400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>2000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>3000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>3000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>5400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>600</v>
+      </c>
+      <c r="F22" s="3">
         <v>400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>600</v>
-      </c>
-      <c r="H22" s="3">
-        <v>700</v>
-      </c>
-      <c r="I22" s="3">
-        <v>700</v>
       </c>
       <c r="J22" s="3">
         <v>700</v>
@@ -1253,39 +1332,45 @@
         <v>700</v>
       </c>
       <c r="L22" s="3">
+        <v>700</v>
+      </c>
+      <c r="M22" s="3">
+        <v>700</v>
+      </c>
+      <c r="N22" s="3">
         <v>800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F23" s="3">
         <v>1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>800</v>
       </c>
       <c r="J23" s="3">
         <v>800</v>
@@ -1294,19 +1379,25 @@
         <v>800</v>
       </c>
       <c r="L23" s="3">
+        <v>800</v>
+      </c>
+      <c r="M23" s="3">
+        <v>800</v>
+      </c>
+      <c r="N23" s="3">
         <v>1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>4000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1346,8 +1437,14 @@
       <c r="O24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,28 +1484,34 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F26" s="3">
         <v>1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>800</v>
-      </c>
-      <c r="I26" s="3">
-        <v>800</v>
       </c>
       <c r="J26" s="3">
         <v>800</v>
@@ -1417,39 +1520,45 @@
         <v>800</v>
       </c>
       <c r="L26" s="3">
+        <v>800</v>
+      </c>
+      <c r="M26" s="3">
+        <v>800</v>
+      </c>
+      <c r="N26" s="3">
         <v>1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>4000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F27" s="3">
         <v>1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>800</v>
-      </c>
-      <c r="I27" s="3">
-        <v>800</v>
       </c>
       <c r="J27" s="3">
         <v>800</v>
@@ -1458,19 +1567,25 @@
         <v>800</v>
       </c>
       <c r="L27" s="3">
+        <v>800</v>
+      </c>
+      <c r="M27" s="3">
+        <v>800</v>
+      </c>
+      <c r="N27" s="3">
         <v>1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>4000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1625,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1672,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1719,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,35 +1766,41 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -1674,28 +1813,34 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F33" s="3">
         <v>1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>800</v>
-      </c>
-      <c r="I33" s="3">
-        <v>800</v>
       </c>
       <c r="J33" s="3">
         <v>800</v>
@@ -1704,19 +1849,25 @@
         <v>800</v>
       </c>
       <c r="L33" s="3">
+        <v>800</v>
+      </c>
+      <c r="M33" s="3">
+        <v>800</v>
+      </c>
+      <c r="N33" s="3">
         <v>1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>4000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,28 +1907,34 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F35" s="3">
         <v>1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>800</v>
-      </c>
-      <c r="I35" s="3">
-        <v>800</v>
       </c>
       <c r="J35" s="3">
         <v>800</v>
@@ -1786,65 +1943,77 @@
         <v>800</v>
       </c>
       <c r="L35" s="3">
+        <v>800</v>
+      </c>
+      <c r="M35" s="3">
+        <v>800</v>
+      </c>
+      <c r="N35" s="3">
         <v>1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>4000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +2029,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,64 +2048,72 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F41" s="3">
         <v>5600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3400</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>10300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>10300</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -1959,49 +2138,61 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>700</v>
+      </c>
+      <c r="F43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>12700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>12700</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2041,22 +2232,28 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>400</v>
+      </c>
+      <c r="F45" s="3">
         <v>1400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>600</v>
       </c>
       <c r="H45" s="3">
         <v>600</v>
@@ -2064,67 +2261,79 @@
       <c r="I45" s="3">
         <v>600</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="J45" s="3">
+        <v>600</v>
+      </c>
+      <c r="K45" s="3">
+        <v>600</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>12600</v>
+      </c>
+      <c r="F46" s="3">
         <v>18400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>18400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>6000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>16600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>16600</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2164,49 +2373,61 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>47900</v>
+      </c>
+      <c r="F48" s="3">
         <v>51300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>51300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>54500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>54500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>57800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>57800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>61100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>61100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>62300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>62300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2246,8 +2467,14 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2514,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,22 +2561,28 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F52" s="3">
         <v>500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>500</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1000</v>
       </c>
       <c r="H52" s="3">
         <v>1000</v>
@@ -2363,14 +2602,20 @@
       <c r="M52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2655,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>63200</v>
+      </c>
+      <c r="F54" s="3">
         <v>70800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>70800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>63300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>63300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>65100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>65100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>69000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>69000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>80200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>80200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2725,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,16 +2744,18 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E57" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="F57" s="3">
         <v>1000</v>
@@ -2509,39 +2770,45 @@
         <v>1000</v>
       </c>
       <c r="J57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F58" s="3">
         <v>6400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>6400</v>
-      </c>
-      <c r="F58" s="3">
-        <v>7900</v>
-      </c>
-      <c r="G58" s="3">
-        <v>7900</v>
       </c>
       <c r="H58" s="3">
         <v>7900</v>
@@ -2550,10 +2817,10 @@
         <v>7900</v>
       </c>
       <c r="J58" s="3">
-        <v>8200</v>
+        <v>7900</v>
       </c>
       <c r="K58" s="3">
-        <v>8200</v>
+        <v>7900</v>
       </c>
       <c r="L58" s="3">
         <v>8200</v>
@@ -2562,136 +2829,160 @@
         <v>8200</v>
       </c>
       <c r="N58" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+        <v>8200</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F59" s="3">
         <v>25500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>25500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>26200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>26200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>26100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>26100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>26900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>26900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>25500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>25500</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>28800</v>
+      </c>
+      <c r="F60" s="3">
         <v>34100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>34100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>35700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>35700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>35400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>35400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>36500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>36500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>34600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>34600</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F61" s="3">
         <v>11900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>11900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>14400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>14400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>18400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>18400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>23100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>23100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>27200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>27200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2707,32 +2998,38 @@
       <c r="G62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
         <v>400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +3069,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +3116,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3163,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>38600</v>
+      </c>
+      <c r="F66" s="3">
         <v>46000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>46000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>50100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>50100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>54200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>54200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>61000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>61000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>62300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>62300</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3233,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3276,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3323,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3370,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3417,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F72" s="3">
         <v>12400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>12400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>10200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>10200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>9300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>9300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>7900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>7900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>17900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>17900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3511,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3558,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3605,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>24600</v>
+      </c>
+      <c r="F76" s="3">
         <v>24800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>24800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>13200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>13200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>10900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>7900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>7900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>18000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>18000</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q76" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,74 +3699,86 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F81" s="3">
         <v>1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>800</v>
-      </c>
-      <c r="I81" s="3">
-        <v>800</v>
       </c>
       <c r="J81" s="3">
         <v>800</v>
@@ -3398,19 +3787,25 @@
         <v>800</v>
       </c>
       <c r="L81" s="3">
+        <v>800</v>
+      </c>
+      <c r="M81" s="3">
+        <v>800</v>
+      </c>
+      <c r="N81" s="3">
         <v>1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>4000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,8 +3821,10 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3438,10 +3835,10 @@
         <v>1700</v>
       </c>
       <c r="F83" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G83" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="H83" s="3">
         <v>1600</v>
@@ -3450,25 +3847,31 @@
         <v>1600</v>
       </c>
       <c r="J83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3911,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3958,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +4005,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +4052,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +4099,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F89" s="3">
         <v>2100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>2100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>4500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,16 +4169,18 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-300</v>
+        <v>-700</v>
       </c>
       <c r="E91" s="3">
-        <v>-300</v>
+        <v>-700</v>
       </c>
       <c r="F91" s="3">
         <v>-300</v>
@@ -3754,10 +4195,10 @@
         <v>-300</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -3766,13 +4207,19 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-6000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4259,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,40 +4306,46 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-5400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-5400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>5600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>5600</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-6000</v>
       </c>
       <c r="N94" s="3">
         <v>-6000</v>
@@ -3894,8 +4353,14 @@
       <c r="O94" s="3">
         <v>-6000</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,8 +4376,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3928,32 +4395,38 @@
       <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>5800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>5800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>1200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4466,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4513,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,49 +4560,61 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F100" s="3">
         <v>3600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>3600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-6900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-6900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-2100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>3800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4157,45 +4654,57 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F102" s="3">
         <v>400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-5800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-5800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>2300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>2300</v>
       </c>
     </row>
